--- a/aq_files/0067.xlsx
+++ b/aq_files/0067.xlsx
@@ -1,101 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Q.No,Question,Type,Difficulty</t>
-  </si>
-  <si>
-    <t>1,What is a Generative Adversarial Network (GAN)? Explain the basic concept.,Theory,Easy</t>
-  </si>
-  <si>
-    <t>2,Who introduced GANs and in which year? What was the original paper?,Theory,Easy</t>
-  </si>
-  <si>
-    <t>3,Explain the roles of the generator and discriminator in a GAN.,Theory,Easy</t>
-  </si>
-  <si>
-    <t>4,What is the adversarial training process in GANs? How do generator and discriminator compete?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>5,Write the mathematical formulation of the GAN objective function (minimax game).,Technical,Medium</t>
-  </si>
-  <si>
-    <t>6,What is the concept of Nash equilibrium in GAN training? How does it relate to convergence?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>7,What are the common challenges in training GANs (mode collapse, non-convergence, vanishing gradients)?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>8,What is mode collapse? Why does it happen and how can it be prevented?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>9,What is the difference between unconditional and conditional GANs? Explain with examples.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>10,What are the different GAN variants (DCGAN, CycleGAN, StyleGAN, Pix2Pix)? Briefly explain each.,Theory,Medium</t>
-  </si>
-  <si>
-    <t>11,What is the role of the latent vector z in GANs? How does it control generation?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>12,How do you evaluate GANs? Discuss metrics like Inception Score (IS) and Fréchet Inception Distance (FID).,Technical,Hard</t>
-  </si>
-  <si>
-    <t>13,What are the differences between GANs and VAEs in terms of architecture and output quality?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>14,Explain the concept of Wasserstein GAN (WGAN). How does it improve training stability?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>15,What is spectral normalization in GANs? How does it help with training?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>16,What are the hardware and computational requirements for training high-resolution GANs?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>17,How do GANs handle discrete data like text? What are the challenges?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>18,What is the difference between GANs and diffusion models for image generation?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>19,What are the ethical concerns surrounding GANs (deepfakes, misuse, bias)?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>20,Write the pseudo-code for training a standard GAN.,Coding,Medium</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -105,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,118 +316,1023 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Component_ID,Component_Name,Component_Category,Primary_Function,Data_Type,Processing_Mode,Storage_Type,Query_Language,Use_Case,Latency_Ms,Throughput_MBps,Data_Volume_TB,Users_Count,Deployment_Type,Integration_Tools,License,Learning_Curve,Popularity_Rank,Cluster_Size_Nodes,Avg_Job_Time_Sec,Fault_Tolerance,Schema_Type</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>H-001,HDFS,Storage,Distributed File Storage,Batch,Batch,Disk,None,Data Storage,50,5000,10000,5000,On-Prem,Sqoop,Apache,Medium,1,128,300,High,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>H-002,MapReduce,Processing,Batch Processing,Batch,Batch,Disk,Java,ETL,5000,2000,5000,3000,On-Prem,Hive/Pig,Apache,High,2,128,600,High,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>H-003,YARN,Resource Management,Cluster Resource Management,Batch,Batch,Memory,None,Resource Scheduling,10,10000,10000,2000,On-Prem,All,Apache,High,3,128,N/A,High,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>H-004,Hive,Data Warehouse,SQL-like Queries on Hadoop,Batch,Batch,Disk,HiveQL,Analytics,3000,1500,8000,4000,On-Prem,Tez/Spark,Apache,Medium,4,64,180,Medium,Schema-on-Read</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>H-005,HBase,NoSQL Database,Real-time Read/Write,Structured,Real-time,Memory/Disk,Java/API,OLTP,10,5000,2000,3500,On-Prem,Spark/Phoenix,Apache,High,5,32,50,High,Schema-on-Write</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>H-006,Spark,Processing,In-memory Processing,Batch/Streaming,Batch/Streaming,Memory,Python/Scala/SQL,ML/Analytics,100,8000,5000,8000,On-Prem/Cloud,Hive/HBase,Apache,Medium,1,64,120,High,Schema-on-Read</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>H-007,Kafka,Streaming,Message Queue,Streaming,Streaming,Disk,Java/API,Real-time Ingestion,5,10000,3000,5000,On-Prem/Cloud,Spark/Flink,Apache,Medium,6,32,10,High,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>H-008,Flume,Ingestion,Log Collection,Streaming,Batch,Disk,Config,Log Aggregation,1000,1000,2000,2000,On-Prem,Kafka/HDFS,Apache,Easy,7,16,60,Medium,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>H-009,Sqoop,Ingestion,Data Import/Export,Batch,Batch,Disk,CLI,RDBMS Integration,2000,500,1000,2500,On-Prem,Hive/HBase,Apache,Medium,8,16,90,Medium,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>H-010,Pig,Processing,Data Flow Scripting,Batch,Batch,Disk,Pig Latin,ETL,4000,1200,3000,1500,On-Prem,HDFS,Apache,Medium,9,32,240,Medium,Schema-on-Read</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>H-011,Impala,Query Engine,Interactive SQL,Batch,Interactive,Memory,SQL,Analytics,200,4000,4000,3000,On-Prem,HDFS/Kudu,Apache,Medium,10,32,45,High,Schema-on-Read</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>H-012,Storm,Streaming,Real-time Processing,Streaming,Streaming,Memory,Java/API,Real-time Analytics,20,2000,500,1000,On-Prem,Kafka,Apache,High,12,16,5,Medium,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>H-013,Oozie,Workflow,Job Scheduling,Batch,Batch,Disk,XML,Workflow Automation,5000,100,1000,1000,On-Prem,Hive/Pig,Apache,Medium,13,16,300,Medium,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>H-014,Zeppelin,Visualization,Notebook Interface,Interactive,Interactive,Memory,SQL/Python,Data Exploration,500,100,500,2000,On-Prem/Cloud,Spark/Hive,Apache,Medium,11,8,30,Medium,N/A</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>H-015,Kudu,Storage,Columnar Storage,Batch/Streaming,Batch/Streaming,Memory/Disk,SQL/API,Real-time Analytics,50,3000,1500,1200,On-Prem,Spark/Impala,Apache,High,14,16,80,High,Schema-on-Write</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>H-016,Phoenix,SQL Layer,SQL on HBase,Batch/Streaming,Batch/Real-time,Memory,SQL,OLTP/OLAP,100,2000,1000,800,On-Prem,HBase,Apache,Medium,15,16,60,High,Schema-on-Write</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>H-017,Atlas,Governance,Data Lineage,Batch,Batch,Disk,REST API,Metadata Management,2000,100,500,500,On-Prem,Hive/HBase,Apache,High,18,8,120,Medium,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>H-018,Ranger,Security,Access Control,Batch,Batch,Disk,REST API,Security Management,100,500,500,1000,On-Prem,Hive/HBase,Apache,Medium,17,8,N/A,High,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>H-019,Tez,Processing,DAG Execution,Batch,Batch,Memory,None,Performance Optimization,3000,2500,3000,800,On-Prem,Hive/Pig,Apache,High,16,32,90,High,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>H-020,Avro,Serialization,Data Serialization,Batch,Batch,Disk,Schema,Data Exchange,100,5000,2000,1500,On-Prem,All,Apache,Medium,19,64,N/A,Medium,Schema-on-Write</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>H-021,Parquet,Storage,Columnar Storage,Batch,Batch,Disk,None,Analytics Optimization,50,4000,4000,2000,On-Prem,Spark/Hive,Apache,Medium,4,64,N/A,High,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>H-022,ORC,Storage,Optimized Row Columnar,Batch,Batch,Disk,None,Analytics Optimization,50,4000,3500,1800,On-Prem,Hive/Spark,Apache,Medium,5,64,N/A,High,Schema-on-Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>H-023,ZooKeeper,Coordination,Distributed Coordination,Batch,Real-time,Memory,None,Configuration Management,10,5000,100,1500,On-Prem,All,Apache,High,20,16,N/A,High,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>H-024,Ambari,Management,Cluster Management,Batch,Batch,Disk,REST API,Monitoring/Admin,5000,100,500,800,On-Prem,All,Apache,Medium,21,16,N/A,Medium,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>H-025,Cloudera Manager,Management,Enterprise Management,Batch,Batch,Disk,REST API,Enterprise Admin,5000,100,1000,2000,On-Prem,All,Cloudera,Medium,22,128,N/A,High,N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>JOB-026,2024-03-01 00:00:26,Fraud_Detection,Interactive,224,112,56,28,42,11,2,234,Prod-Cluster,Active,128,128,3,47,69,64,360,300,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>JOB-027,2024-03-01 00:00:27,Log_Archival,ETL,1536,768,384,192,288,72,7,1490,Prod-Cluster,Active,128,128,3,51,84,79,740,660,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>JOB-028,2024-03-01 00:00:28,User_Engagement,Batch,432,216,108,54,81,20,3,445,Prod-Cluster,Active,128,128,3,48,70,65,470,400,Priority,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>JOB-029,2024-03-01 00:00:29,Real_Time_Alert,Streaming,36,18,9,5,7,2,0,41,Prod-Cluster,Active,128,128,3,46,56,51,170,140,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>JOB-030,2024-03-01 00:00:30,Backup_Operation,ETL,2560,1280,640,320,480,120,9,2450,Prod-Cluster,Active,128,128,3,53,90,88,950,840,Default,Low,Failed,NameNode_Timeout</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What are the core components of Hadoop? Identify HDFS, MapReduce, and YARN from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Component_Name, Component_Category | HDFS (Storage), MapReduce (Processing), YARN (Resource Management). These form the foundation of Hadoop</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Core components provide distributed storage, processing, and resource management</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between HDFS, MapReduce, and YARN? Compare their primary functions and latency.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Compare Primary_Function, Latency_Ms | HDFS: Storage (50ms), MapReduce: Batch processing (5000ms), YARN: Resource scheduling (10ms). YARN has lowest latency</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>HDFS stores data; MapReduce processes; YARN manages resources</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is Hive and what problem does it solve? Analyze its use case and latency.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Component_Name, Use_Case, Latency_Ms | Hive enables SQL queries on Hadoop (HiveQL). Latency: 3000ms. Used for analytics and reporting</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Hive bridges SQL and Hadoop, making Big Data accessible to analysts</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is HBase and how does it differ from Hive? Compare their processing modes and latency.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Compare Processing_Mode, Latency_Ms, Use_Case | HBase: Real-time OLTP (10ms latency); Hive: Batch analytics (3000ms latency). HBase for low-latency access</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>HBase for real-time; Hive for batch analytics</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is Spark and how does it improve upon MapReduce? Compare their processing modes and latency.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Compare Processing_Mode, Latency_Ms, Throughput_MBps | Spark: In-memory processing (100ms latency, 8000 MBps); MapReduce: Disk-based (5000ms latency, 2000 MBps)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Spark's in-memory processing is 50x faster than MapReduce</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is Kafka and what role does it play in data ingestion? Analyze its latency and throughput.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Latency_Ms, Throughput_MBps, Use_Case | Kafka: 5ms latency, 10,000 MBps throughput. Used for real-time data ingestion and message queuing</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Kafka enables real-time data streaming at massive scale</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between batch processing and stream processing? Compare MapReduce vs Kafka/Storm.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Compare Processing_Mode across components | Batch: MapReduce, Hive (seconds to hours); Stream: Kafka, Storm (milliseconds to seconds)</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Different workloads require different processing modes</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What are the main data ingestion tools in Hadoop? Identify Flume, Sqoop, and Kafka.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Component_Category = Ingestion | Flume: Log collection (1000ms latency); Sqoop: RDBMS import/export (2000ms); Kafka: Real-time streaming (5ms)</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Choose ingestion tool based on data source and latency requirements</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between schema-on-read and schema-on-write? Identify components for each.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Schema_Type column | Schema-on-Read: Hive, Spark, Impala (flexible); Schema-on-Write: HBase, Kudu, Phoenix (structured)</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Schema-on-read offers flexibility; schema-on-write offers performance</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What are the main storage formats in Hadoop? Compare Avro, Parquet, and ORC.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Component_Name where Category=Storage | Avro: Row-based serialization; Parquet: Columnar, high compression; ORC: Optimized for Hive queries</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Choose format based on use case: Avro for serialization, Parquet/ORC for analytics</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is Impala and how does it compare to Hive for query performance?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Compare Latency_Ms, Throughput_MBps | Impala: 200ms latency (interactive); Hive: 3000ms latency (batch). Impala is 15x faster for queries</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Impala provides interactive SQL on Hadoop</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What are the main workflow and scheduling tools? Identify Oozie and its capabilities.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Oozie's Use_Case, Avg_Job_Time_Sec | Oozie: Job scheduling and workflow automation (300 sec average job time)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Oozie orchestrates complex data pipelines</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What are the security and governance components? Identify Ranger and Atlas.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Ranger and Atlas functions | Ranger: Access control, security policies; Atlas: Data lineage, metadata management</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Security and governance are critical for enterprise Hadoop deployments</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is ZooKeeper and why is it important? Analyze its role in coordination.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Analyze ZooKeeper's Primary_Function, Latency_Ms | ZooKeeper: Distributed coordination (10ms latency). Used for configuration management, leader election</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>ZooKeeper provides reliable distributed coordination</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What are the main visualization and exploration tools? Identify Zeppelin and its features.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Zeppelin's Use_Case, Query_Language | Zeppelin: Notebook interface for data exploration (SQL/Python), 500ms latency</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Zeppelin enables interactive data exploration and collaboration</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between HBase and Kudu? Compare their use cases and storage characteristics.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Compare HBase and Kudu metrics | HBase: NoSQL, real-time OLTP (10ms); Kudu: Columnar storage for real-time analytics (50ms)</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>HBase for key-value lookups; Kudu for real-time analytics</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What are the main SQL-on-Hadoop engines? Identify Hive, Impala, Phoenix, and Spark SQL.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Identify components with SQL query language | Hive (HiveQL), Impala (SQL), Phoenix (SQL on HBase), Spark (SQL)</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Multiple SQL engines for different use cases and performance requirements</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What are the popular Hadoop distributions? Identify Cloudera Manager and Ambari.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Deployment_Type, License | Cloudera Manager: Enterprise management; Ambari: Open-source cluster management; Both for administration</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Distributions provide enterprise features and management tools</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the average latency for different processing modes: Batch, Real-time, Interactive, Streaming.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Group by Processing_Mode; Average Latency | Batch: 3,250ms; Real-time: 53ms; Interactive: 350ms; Streaming: 8ms</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Processing mode determines latency expectations</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Components of Hadoop Ecosystem</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Hadoop ecosystem reference architecture mapping components to layers: Ingestion, Storage, Processing, Query, Visualization.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Map components to architecture layers | Ingestion: Kafka, Flume, Sqoop; Storage: HDFS, HBase, Kudu; Processing: Spark, MapReduce; Query: Hive, Impala; Visualization: Zeppelin</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Ecosystem components work together in layered architecture</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>